--- a/public/modelo-leads.xlsx
+++ b/public/modelo-leads.xlsx
@@ -639,7 +639,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pet shop,Veterinária,Barbearia,Salão de beleza,Estética,Unhas"</formula1>
+      <formula1>"Pet shop,Veterinária,Barbearia,Salão de beleza,Estética,Unhas,Tatuagem"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -665,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -675,7 +676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Categoria: pet shop, veterinária, barbearia, salão, estética ou unhas. Outros ramos ficam de fora.</t>
+          <t>Categoria: pet shop, veterinária, barbearia, salão, estética, unhas ou tatuagem. Outros ramos ficam de fora.</t>
         </is>
       </c>
     </row>

--- a/public/modelo-leads.xlsx
+++ b/public/modelo-leads.xlsx
@@ -639,7 +639,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pet shop,Veterinária,Barbearia,Salão de beleza,Estética,Unhas,Tatuagem"</formula1>
+      <formula1>"Pet shop,Veterinária,Barbearia,Salão de beleza,Estética,Unhas,Tatuagem,Odontologia,Fisioterapia,Psicologia,Nutrição,Clínica médica,Escola de idiomas,Reforço escolar,Escola de música,Autoescola,Academia,Pilates,Lutas,Dança,Oficina mecânica,Estética automotiva,Pneus"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -676,7 +676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Categoria: pet shop, veterinária, barbearia, salão, estética, unhas ou tatuagem. Outros ramos ficam de fora.</t>
+          <t>Categoria: pet, beleza (barbearia, salão, estética, unhas, tatuagem), saúde (odontologia, fisioterapia, psicologia, nutrição, clínica), aulas (idiomas, reforço, música, autoescola), fitness (academia, pilates, lutas, dança) ou automotivo (oficina, estética automotiva, pneus).</t>
         </is>
       </c>
     </row>
